--- a/excel/sample_excel_file.xlsx
+++ b/excel/sample_excel_file.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Git Project\Warehouse\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Git Project\Warehouse\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8464D3-6FCB-416E-86FD-16EFB21AB53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6973421A-5C6A-48A7-8955-14280FC95F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29505" yWindow="1140" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30150" yWindow="1800" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>project_code</t>
   </si>
@@ -36,9 +36,6 @@
     <t>row</t>
   </si>
   <si>
-    <t>first_recipient_delivery</t>
-  </si>
-  <si>
     <t>company</t>
   </si>
   <si>
@@ -66,15 +63,6 @@
     <t>property_code</t>
   </si>
   <si>
-    <t>second_recipient_delivery</t>
-  </si>
-  <si>
-    <t>third_recipient_delivery</t>
-  </si>
-  <si>
-    <t>forth_recipient_delivery</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
@@ -82,6 +70,12 @@
   </si>
   <si>
     <t>closed_time</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>recipient_delivery</t>
   </si>
 </sst>
 </file>
@@ -408,10 +402,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -422,52 +416,46 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
